--- a/output/yearly_population_iteration_56_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_56_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5482</v>
+        <v>5210</v>
       </c>
       <c r="C2" t="n">
-        <v>9977</v>
+        <v>12912</v>
       </c>
       <c r="D2" t="n">
-        <v>26179</v>
+        <v>19157</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3667</v>
+        <v>3191</v>
       </c>
       <c r="C3" t="n">
-        <v>4663</v>
+        <v>4542</v>
       </c>
       <c r="D3" t="n">
-        <v>17500</v>
+        <v>11541</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2921</v>
+        <v>2632</v>
       </c>
       <c r="C4" t="n">
-        <v>4279</v>
+        <v>3841</v>
       </c>
       <c r="D4" t="n">
-        <v>8626</v>
+        <v>6129</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1924</v>
+        <v>1738</v>
       </c>
       <c r="C5" t="n">
-        <v>3564</v>
+        <v>3660</v>
       </c>
       <c r="D5" t="n">
-        <v>3387</v>
+        <v>2536</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1138</v>
+        <v>1003</v>
       </c>
       <c r="C6" t="n">
-        <v>2562</v>
+        <v>3084</v>
       </c>
       <c r="D6" t="n">
-        <v>1353</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>530</v>
+        <v>461</v>
       </c>
       <c r="C7" t="n">
-        <v>1494</v>
+        <v>2116</v>
       </c>
       <c r="D7" t="n">
-        <v>695</v>
+        <v>658</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>196</v>
+        <v>172</v>
       </c>
       <c r="C8" t="n">
-        <v>613</v>
+        <v>1072</v>
       </c>
       <c r="D8" t="n">
-        <v>435</v>
+        <v>432</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C9" t="n">
-        <v>270</v>
+        <v>450</v>
       </c>
       <c r="D9" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>201</v>
+        <v>227</v>
       </c>
       <c r="D10" t="n">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
         <v>166</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12">
@@ -926,7 +926,7 @@
         <v>129</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -965,7 +965,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -982,7 +982,7 @@
         <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1007,7 +1007,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7330</v>
+        <v>6762</v>
       </c>
       <c r="C2" t="n">
-        <v>11540</v>
+        <v>18969</v>
       </c>
       <c r="D2" t="n">
-        <v>35122</v>
+        <v>16528</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3654</v>
+        <v>3327</v>
       </c>
       <c r="C3" t="n">
-        <v>6264</v>
+        <v>7404</v>
       </c>
       <c r="D3" t="n">
-        <v>17504</v>
+        <v>11801</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2780</v>
+        <v>2464</v>
       </c>
       <c r="C4" t="n">
-        <v>4378</v>
+        <v>4104</v>
       </c>
       <c r="D4" t="n">
-        <v>9729</v>
+        <v>6767</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2104</v>
+        <v>1882</v>
       </c>
       <c r="C5" t="n">
-        <v>3791</v>
+        <v>3633</v>
       </c>
       <c r="D5" t="n">
-        <v>4139</v>
+        <v>3045</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1345</v>
+        <v>1216</v>
       </c>
       <c r="C6" t="n">
-        <v>2998</v>
+        <v>3318</v>
       </c>
       <c r="D6" t="n">
-        <v>1634</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>708</v>
+        <v>620</v>
       </c>
       <c r="C7" t="n">
-        <v>1960</v>
+        <v>2530</v>
       </c>
       <c r="D7" t="n">
-        <v>791</v>
+        <v>730</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>297</v>
+        <v>259</v>
       </c>
       <c r="C8" t="n">
-        <v>1001</v>
+        <v>1531</v>
       </c>
       <c r="D8" t="n">
-        <v>464</v>
+        <v>456</v>
       </c>
     </row>
     <row r="9">
@@ -1189,10 +1189,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>411</v>
+        <v>707</v>
       </c>
       <c r="D9" t="n">
         <v>323</v>
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>229</v>
+        <v>318</v>
       </c>
       <c r="D10" t="n">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="D11" t="n">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -1265,7 +1265,7 @@
         <v>82</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -1293,7 +1293,7 @@
         <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8613</v>
+        <v>9231</v>
       </c>
       <c r="C2" t="n">
-        <v>10217</v>
+        <v>18945</v>
       </c>
       <c r="D2" t="n">
-        <v>35480</v>
+        <v>19237</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4217</v>
+        <v>3838</v>
       </c>
       <c r="C3" t="n">
-        <v>7493</v>
+        <v>10818</v>
       </c>
       <c r="D3" t="n">
-        <v>18610</v>
+        <v>11631</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2675</v>
+        <v>2428</v>
       </c>
       <c r="C4" t="n">
-        <v>5077</v>
+        <v>5436</v>
       </c>
       <c r="D4" t="n">
-        <v>10627</v>
+        <v>7334</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2120</v>
+        <v>1889</v>
       </c>
       <c r="C5" t="n">
-        <v>3965</v>
+        <v>3726</v>
       </c>
       <c r="D5" t="n">
-        <v>4778</v>
+        <v>3459</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1507</v>
+        <v>1356</v>
       </c>
       <c r="C6" t="n">
-        <v>3268</v>
+        <v>3420</v>
       </c>
       <c r="D6" t="n">
-        <v>1973</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>866</v>
+        <v>771</v>
       </c>
       <c r="C7" t="n">
-        <v>2367</v>
+        <v>2828</v>
       </c>
       <c r="D7" t="n">
-        <v>890</v>
+        <v>799</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>409</v>
+        <v>355</v>
       </c>
       <c r="C8" t="n">
-        <v>1385</v>
+        <v>1931</v>
       </c>
       <c r="D8" t="n">
-        <v>504</v>
+        <v>488</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="C9" t="n">
-        <v>632</v>
+        <v>1014</v>
       </c>
       <c r="D9" t="n">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>296</v>
+        <v>459</v>
       </c>
       <c r="D10" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>194</v>
+        <v>235</v>
       </c>
       <c r="D11" t="n">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D12" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
@@ -1562,7 +1562,7 @@
         <v>119</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14">
@@ -1576,7 +1576,7 @@
         <v>89</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15">
@@ -1587,7 +1587,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7798</v>
+        <v>8211</v>
       </c>
       <c r="C2" t="n">
-        <v>6865</v>
+        <v>12731</v>
       </c>
       <c r="D2" t="n">
-        <v>29098</v>
+        <v>15836</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4973</v>
+        <v>4521</v>
       </c>
       <c r="C3" t="n">
-        <v>10548</v>
+        <v>15002</v>
       </c>
       <c r="D3" t="n">
-        <v>20313</v>
+        <v>12901</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1958</v>
+        <v>1745</v>
       </c>
       <c r="C4" t="n">
-        <v>6633</v>
+        <v>6603</v>
       </c>
       <c r="D4" t="n">
-        <v>10296</v>
+        <v>7215</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1392</v>
+        <v>1252</v>
       </c>
       <c r="C5" t="n">
-        <v>3202</v>
+        <v>3351</v>
       </c>
       <c r="D5" t="n">
-        <v>3263</v>
+        <v>2502</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>800</v>
+        <v>712</v>
       </c>
       <c r="C6" t="n">
-        <v>2319</v>
+        <v>2771</v>
       </c>
       <c r="D6" t="n">
-        <v>872</v>
+        <v>783</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>377</v>
+        <v>328</v>
       </c>
       <c r="C7" t="n">
-        <v>1357</v>
+        <v>1892</v>
       </c>
       <c r="D7" t="n">
-        <v>493</v>
+        <v>478</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>619</v>
+        <v>993</v>
       </c>
       <c r="D8" t="n">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>290</v>
+        <v>449</v>
       </c>
       <c r="D9" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="10">
@@ -1828,10 +1828,10 @@
         <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>230</v>
       </c>
       <c r="D10" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12">
@@ -1859,7 +1859,7 @@
         <v>116</v>
       </c>
       <c r="D12" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13">
@@ -1873,7 +1873,7 @@
         <v>87</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -1884,7 +1884,7 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
         <v>77</v>
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4754</v>
+        <v>4756</v>
       </c>
       <c r="C2" t="n">
-        <v>3344</v>
+        <v>6089</v>
       </c>
       <c r="D2" t="n">
-        <v>20155</v>
+        <v>11577</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5311</v>
+        <v>5235</v>
       </c>
       <c r="C3" t="n">
-        <v>8020</v>
+        <v>12641</v>
       </c>
       <c r="D3" t="n">
-        <v>20337</v>
+        <v>12557</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2734</v>
+        <v>2424</v>
       </c>
       <c r="C4" t="n">
-        <v>8591</v>
+        <v>10670</v>
       </c>
       <c r="D4" t="n">
-        <v>11719</v>
+        <v>8007</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1523</v>
+        <v>1366</v>
       </c>
       <c r="C5" t="n">
-        <v>4705</v>
+        <v>4784</v>
       </c>
       <c r="D5" t="n">
-        <v>4104</v>
+        <v>3062</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>957</v>
+        <v>853</v>
       </c>
       <c r="C6" t="n">
-        <v>2742</v>
+        <v>3113</v>
       </c>
       <c r="D6" t="n">
-        <v>1116</v>
+        <v>961</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>353</v>
+        <v>309</v>
       </c>
       <c r="C7" t="n">
-        <v>1740</v>
+        <v>2299</v>
       </c>
       <c r="D7" t="n">
-        <v>542</v>
+        <v>522</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="C8" t="n">
-        <v>828</v>
+        <v>1280</v>
       </c>
       <c r="D8" t="n">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C9" t="n">
-        <v>340</v>
+        <v>511</v>
       </c>
       <c r="D9" t="n">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>213</v>
+        <v>244</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
+        <v>169</v>
+      </c>
+      <c r="D11" t="n">
         <v>167</v>
-      </c>
-      <c r="D11" t="n">
-        <v>166</v>
       </c>
     </row>
     <row r="12">
@@ -2170,7 +2170,7 @@
         <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4889</v>
+        <v>4023</v>
       </c>
       <c r="C2" t="n">
-        <v>6628</v>
+        <v>8699</v>
       </c>
       <c r="D2" t="n">
-        <v>22340</v>
+        <v>10489</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4259</v>
+        <v>4267</v>
       </c>
       <c r="C3" t="n">
-        <v>5086</v>
+        <v>8479</v>
       </c>
       <c r="D3" t="n">
-        <v>19106</v>
+        <v>11672</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3321</v>
+        <v>3088</v>
       </c>
       <c r="C4" t="n">
-        <v>8209</v>
+        <v>11413</v>
       </c>
       <c r="D4" t="n">
-        <v>12769</v>
+        <v>8506</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1809</v>
+        <v>1613</v>
       </c>
       <c r="C5" t="n">
-        <v>6435</v>
+        <v>7453</v>
       </c>
       <c r="D5" t="n">
-        <v>5109</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1099</v>
+        <v>982</v>
       </c>
       <c r="C6" t="n">
-        <v>3627</v>
+        <v>3866</v>
       </c>
       <c r="D6" t="n">
-        <v>1570</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>523</v>
+        <v>462</v>
       </c>
       <c r="C7" t="n">
-        <v>2171</v>
+        <v>2671</v>
       </c>
       <c r="D7" t="n">
-        <v>615</v>
+        <v>576</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>177</v>
+        <v>158</v>
       </c>
       <c r="C8" t="n">
-        <v>1211</v>
+        <v>1701</v>
       </c>
       <c r="D8" t="n">
-        <v>363</v>
+        <v>359</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C9" t="n">
-        <v>533</v>
+        <v>802</v>
       </c>
       <c r="D9" t="n">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>258</v>
+        <v>340</v>
       </c>
       <c r="D10" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -2551,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2914</v>
+        <v>2392</v>
       </c>
       <c r="C2" t="n">
-        <v>3094</v>
+        <v>4071</v>
       </c>
       <c r="D2" t="n">
-        <v>15575</v>
+        <v>7322</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4254</v>
+        <v>4096</v>
       </c>
       <c r="C3" t="n">
-        <v>5400</v>
+        <v>8295</v>
       </c>
       <c r="D3" t="n">
-        <v>19014</v>
+        <v>11287</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3671</v>
+        <v>3401</v>
       </c>
       <c r="C4" t="n">
-        <v>7855</v>
+        <v>11313</v>
       </c>
       <c r="D4" t="n">
-        <v>13590</v>
+        <v>8965</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1905</v>
+        <v>1700</v>
       </c>
       <c r="C5" t="n">
-        <v>7718</v>
+        <v>9434</v>
       </c>
       <c r="D5" t="n">
-        <v>5392</v>
+        <v>3922</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>930</v>
+        <v>826</v>
       </c>
       <c r="C6" t="n">
-        <v>4428</v>
+        <v>4782</v>
       </c>
       <c r="D6" t="n">
-        <v>1520</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>163</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>2253</v>
+        <v>2903</v>
       </c>
       <c r="D7" t="n">
-        <v>608</v>
+        <v>578</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>902</v>
+        <v>1302</v>
       </c>
       <c r="D8" t="n">
-        <v>380</v>
+        <v>377</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>252</v>
+        <v>333</v>
       </c>
       <c r="D9" t="n">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="D10" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D11" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -2848,7 +2848,7 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4258</v>
+        <v>2659</v>
       </c>
       <c r="C2" t="n">
-        <v>3090</v>
+        <v>6586</v>
       </c>
       <c r="D2" t="n">
-        <v>15953</v>
+        <v>12362</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3166</v>
+        <v>2913</v>
       </c>
       <c r="C3" t="n">
-        <v>3881</v>
+        <v>5689</v>
       </c>
       <c r="D3" t="n">
-        <v>17268</v>
+        <v>10097</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3415</v>
+        <v>3244</v>
       </c>
       <c r="C4" t="n">
-        <v>6536</v>
+        <v>9766</v>
       </c>
       <c r="D4" t="n">
-        <v>14192</v>
+        <v>9049</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2322</v>
+        <v>2098</v>
       </c>
       <c r="C5" t="n">
-        <v>7693</v>
+        <v>10158</v>
       </c>
       <c r="D5" t="n">
-        <v>6408</v>
+        <v>4528</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1190</v>
+        <v>1044</v>
       </c>
       <c r="C6" t="n">
-        <v>5820</v>
+        <v>6706</v>
       </c>
       <c r="D6" t="n">
-        <v>2020</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>349</v>
+        <v>311</v>
       </c>
       <c r="C7" t="n">
-        <v>3170</v>
+        <v>3666</v>
       </c>
       <c r="D7" t="n">
-        <v>723</v>
+        <v>660</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>1409</v>
+        <v>1920</v>
       </c>
       <c r="D8" t="n">
-        <v>404</v>
+        <v>398</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>469</v>
+        <v>643</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>208</v>
+        <v>237</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11">
@@ -3086,7 +3086,7 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D11" t="n">
         <v>135</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3145,7 +3145,7 @@
         <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2939</v>
+        <v>1874</v>
       </c>
       <c r="C2" t="n">
-        <v>2159</v>
+        <v>3609</v>
       </c>
       <c r="D2" t="n">
-        <v>12321</v>
+        <v>9143</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3080</v>
+        <v>2485</v>
       </c>
       <c r="C3" t="n">
-        <v>3273</v>
+        <v>5540</v>
       </c>
       <c r="D3" t="n">
-        <v>16170</v>
+        <v>9916</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3049</v>
+        <v>2875</v>
       </c>
       <c r="C4" t="n">
-        <v>5455</v>
+        <v>8145</v>
       </c>
       <c r="D4" t="n">
-        <v>14310</v>
+        <v>8991</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2535</v>
+        <v>2313</v>
       </c>
       <c r="C5" t="n">
-        <v>7406</v>
+        <v>10197</v>
       </c>
       <c r="D5" t="n">
-        <v>7232</v>
+        <v>4911</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1393</v>
+        <v>1223</v>
       </c>
       <c r="C6" t="n">
-        <v>6640</v>
+        <v>8017</v>
       </c>
       <c r="D6" t="n">
-        <v>2414</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>326</v>
+        <v>278</v>
       </c>
       <c r="C7" t="n">
-        <v>4035</v>
+        <v>4631</v>
       </c>
       <c r="D7" t="n">
-        <v>832</v>
+        <v>729</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="C8" t="n">
-        <v>1827</v>
+        <v>2376</v>
       </c>
       <c r="D8" t="n">
-        <v>417</v>
+        <v>410</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>555</v>
+        <v>724</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
         <v>136</v>
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3442,7 +3442,7 @@
         <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4928</v>
+        <v>2918</v>
       </c>
       <c r="C2" t="n">
-        <v>6740</v>
+        <v>12582</v>
       </c>
       <c r="D2" t="n">
-        <v>13939</v>
+        <v>11376</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2549</v>
+        <v>1915</v>
       </c>
       <c r="C3" t="n">
-        <v>2536</v>
+        <v>4301</v>
       </c>
       <c r="D3" t="n">
-        <v>14673</v>
+        <v>9188</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2659</v>
+        <v>2382</v>
       </c>
       <c r="C4" t="n">
-        <v>4419</v>
+        <v>6900</v>
       </c>
       <c r="D4" t="n">
-        <v>14142</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2499</v>
+        <v>2304</v>
       </c>
       <c r="C5" t="n">
-        <v>6465</v>
+        <v>9177</v>
       </c>
       <c r="D5" t="n">
-        <v>7963</v>
+        <v>5310</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1652</v>
+        <v>1466</v>
       </c>
       <c r="C6" t="n">
-        <v>6878</v>
+        <v>8767</v>
       </c>
       <c r="D6" t="n">
-        <v>2960</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>586</v>
+        <v>500</v>
       </c>
       <c r="C7" t="n">
-        <v>5003</v>
+        <v>5856</v>
       </c>
       <c r="D7" t="n">
-        <v>1025</v>
+        <v>854</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="C8" t="n">
-        <v>2623</v>
+        <v>3171</v>
       </c>
       <c r="D8" t="n">
-        <v>465</v>
+        <v>440</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>971</v>
+        <v>1241</v>
       </c>
       <c r="D9" t="n">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>317</v>
+        <v>387</v>
       </c>
       <c r="D10" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11">
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="D11" t="n">
         <v>139</v>
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
         <v>64</v>
@@ -3753,7 +3753,7 @@
         <v>39</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6187</v>
+        <v>4826</v>
       </c>
       <c r="C2" t="n">
-        <v>1823</v>
+        <v>10480</v>
       </c>
       <c r="D2" t="n">
-        <v>22521</v>
+        <v>10958</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3523</v>
+        <v>2111</v>
       </c>
       <c r="C2" t="n">
-        <v>3828</v>
+        <v>7347</v>
       </c>
       <c r="D2" t="n">
-        <v>10259</v>
+        <v>8463</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3443</v>
+        <v>2656</v>
       </c>
       <c r="C3" t="n">
-        <v>3730</v>
+        <v>6475</v>
       </c>
       <c r="D3" t="n">
-        <v>15928</v>
+        <v>10052</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3667</v>
+        <v>3324</v>
       </c>
       <c r="C4" t="n">
-        <v>6496</v>
+        <v>9990</v>
       </c>
       <c r="D4" t="n">
-        <v>14537</v>
+        <v>9175</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1595</v>
+        <v>1397</v>
       </c>
       <c r="C5" t="n">
-        <v>9612</v>
+        <v>12773</v>
       </c>
       <c r="D5" t="n">
-        <v>7183</v>
+        <v>4930</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>541</v>
+        <v>462</v>
       </c>
       <c r="C6" t="n">
-        <v>6251</v>
+        <v>7371</v>
       </c>
       <c r="D6" t="n">
-        <v>2324</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="C7" t="n">
-        <v>2570</v>
+        <v>3107</v>
       </c>
       <c r="D7" t="n">
-        <v>586</v>
+        <v>539</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
-        <v>951</v>
+        <v>1216</v>
       </c>
       <c r="D8" t="n">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>310</v>
+        <v>379</v>
       </c>
       <c r="D9" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10">
@@ -4316,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="D10" t="n">
         <v>136</v>
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D11" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12">
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D12" t="n">
         <v>62</v>
@@ -4361,7 +4361,7 @@
         <v>38</v>
       </c>
       <c r="D13" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7370</v>
+        <v>6915</v>
       </c>
       <c r="C2" t="n">
-        <v>7303</v>
+        <v>6147</v>
       </c>
       <c r="D2" t="n">
-        <v>22479</v>
+        <v>17464</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2628</v>
+        <v>2051</v>
       </c>
       <c r="C3" t="n">
-        <v>918</v>
+        <v>5281</v>
       </c>
       <c r="D3" t="n">
-        <v>4422</v>
+        <v>2480</v>
       </c>
     </row>
     <row r="4">
@@ -4557,7 +4557,7 @@
         <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4571,7 +4571,7 @@
         <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="D6" t="n">
         <v>816</v>
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C8" t="n">
         <v>260</v>
@@ -4610,7 +4610,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C9" t="n">
         <v>205</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5560</v>
+        <v>5273</v>
       </c>
       <c r="C2" t="n">
-        <v>7099</v>
+        <v>5594</v>
       </c>
       <c r="D2" t="n">
-        <v>22569</v>
+        <v>18101</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4104</v>
+        <v>3677</v>
       </c>
       <c r="C3" t="n">
-        <v>3907</v>
+        <v>4976</v>
       </c>
       <c r="D3" t="n">
-        <v>7130</v>
+        <v>4814</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1176</v>
+        <v>925</v>
       </c>
       <c r="C4" t="n">
-        <v>583</v>
+        <v>3138</v>
       </c>
       <c r="D4" t="n">
-        <v>2072</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D5" t="n">
         <v>1198</v>
@@ -4896,7 +4896,7 @@
         <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
         <v>584</v>
@@ -4907,7 +4907,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C8" t="n">
         <v>307</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5025,7 +5025,7 @@
         <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>67</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5558</v>
+        <v>4560</v>
       </c>
       <c r="C2" t="n">
-        <v>5217</v>
+        <v>7054</v>
       </c>
       <c r="D2" t="n">
-        <v>24295</v>
+        <v>19523</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3962</v>
+        <v>3664</v>
       </c>
       <c r="C3" t="n">
-        <v>4888</v>
+        <v>4598</v>
       </c>
       <c r="D3" t="n">
-        <v>9086</v>
+        <v>6593</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2244</v>
+        <v>1952</v>
       </c>
       <c r="C4" t="n">
-        <v>2453</v>
+        <v>4113</v>
       </c>
       <c r="D4" t="n">
-        <v>2980</v>
+        <v>2231</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>533</v>
+        <v>432</v>
       </c>
       <c r="C5" t="n">
-        <v>414</v>
+        <v>1811</v>
       </c>
       <c r="D5" t="n">
-        <v>1309</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="6">
@@ -5193,7 +5193,7 @@
         <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="D6" t="n">
         <v>908</v>
@@ -5207,10 +5207,10 @@
         <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D7" t="n">
-        <v>620</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>460</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -5232,7 +5232,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C9" t="n">
         <v>268</v>
@@ -5249,7 +5249,7 @@
         <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5263,7 +5263,7 @@
         <v>46</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5305,7 +5305,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
         <v>148</v>
@@ -5316,10 +5316,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5336,7 +5336,7 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5957</v>
+        <v>5529</v>
       </c>
       <c r="C2" t="n">
-        <v>4882</v>
+        <v>4803</v>
       </c>
       <c r="D2" t="n">
-        <v>28504</v>
+        <v>20406</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3878</v>
+        <v>3363</v>
       </c>
       <c r="C3" t="n">
-        <v>4401</v>
+        <v>5102</v>
       </c>
       <c r="D3" t="n">
-        <v>10758</v>
+        <v>8094</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2638</v>
+        <v>2350</v>
       </c>
       <c r="C4" t="n">
-        <v>3711</v>
+        <v>4288</v>
       </c>
       <c r="D4" t="n">
-        <v>4003</v>
+        <v>2958</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1136</v>
+        <v>971</v>
       </c>
       <c r="C5" t="n">
-        <v>1458</v>
+        <v>2966</v>
       </c>
       <c r="D5" t="n">
-        <v>1545</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>296</v>
+        <v>254</v>
       </c>
       <c r="C6" t="n">
-        <v>355</v>
+        <v>1050</v>
       </c>
       <c r="D6" t="n">
-        <v>964</v>
+        <v>952</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>143</v>
       </c>
       <c r="C7" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>655</v>
+        <v>660</v>
       </c>
     </row>
     <row r="8">
@@ -5532,10 +5532,10 @@
         <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="D8" t="n">
-        <v>481</v>
+        <v>478</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="D9" t="n">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11">
@@ -5574,7 +5574,7 @@
         <v>49</v>
       </c>
       <c r="C11" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
         <v>286</v>
@@ -5585,10 +5585,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D12" t="n">
         <v>217</v>
@@ -5616,7 +5616,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
         <v>148</v>
@@ -5630,7 +5630,7 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D15" t="n">
         <v>122</v>
@@ -5647,7 +5647,7 @@
         <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6344</v>
+        <v>5987</v>
       </c>
       <c r="C2" t="n">
-        <v>6879</v>
+        <v>5518</v>
       </c>
       <c r="D2" t="n">
-        <v>30165</v>
+        <v>19455</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3553</v>
+        <v>3206</v>
       </c>
       <c r="C3" t="n">
-        <v>3806</v>
+        <v>4054</v>
       </c>
       <c r="D3" t="n">
-        <v>11946</v>
+        <v>8839</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2009</v>
+        <v>1775</v>
       </c>
       <c r="C4" t="n">
-        <v>3323</v>
+        <v>3879</v>
       </c>
       <c r="D4" t="n">
-        <v>4459</v>
+        <v>3318</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>987</v>
+        <v>853</v>
       </c>
       <c r="C5" t="n">
-        <v>1940</v>
+        <v>2643</v>
       </c>
       <c r="D5" t="n">
-        <v>1545</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>335</v>
+        <v>287</v>
       </c>
       <c r="C6" t="n">
-        <v>613</v>
+        <v>1358</v>
       </c>
       <c r="D6" t="n">
-        <v>809</v>
+        <v>777</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C7" t="n">
-        <v>224</v>
+        <v>443</v>
       </c>
       <c r="D7" t="n">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D8" t="n">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D9" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="12">
@@ -5896,7 +5896,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
         <v>91</v>
@@ -5913,10 +5913,10 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14">
@@ -5930,7 +5930,7 @@
         <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15">
@@ -5941,7 +5941,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -5969,7 +5969,7 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
         <v>50</v>
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
         <v>33</v>
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5765</v>
+        <v>4935</v>
       </c>
       <c r="C2" t="n">
-        <v>5525</v>
+        <v>4650</v>
       </c>
       <c r="D2" t="n">
-        <v>30801</v>
+        <v>20408</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4112</v>
+        <v>3822</v>
       </c>
       <c r="C3" t="n">
-        <v>4837</v>
+        <v>4221</v>
       </c>
       <c r="D3" t="n">
-        <v>14368</v>
+        <v>9971</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2443</v>
+        <v>2188</v>
       </c>
       <c r="C4" t="n">
-        <v>3550</v>
+        <v>3904</v>
       </c>
       <c r="D4" t="n">
-        <v>5790</v>
+        <v>4298</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1328</v>
+        <v>1165</v>
       </c>
       <c r="C5" t="n">
-        <v>2722</v>
+        <v>3286</v>
       </c>
       <c r="D5" t="n">
-        <v>2085</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>616</v>
+        <v>531</v>
       </c>
       <c r="C6" t="n">
-        <v>1369</v>
+        <v>2081</v>
       </c>
       <c r="D6" t="n">
-        <v>930</v>
+        <v>855</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>195</v>
+        <v>171</v>
       </c>
       <c r="C7" t="n">
-        <v>445</v>
+        <v>962</v>
       </c>
       <c r="D7" t="n">
-        <v>564</v>
+        <v>560</v>
       </c>
     </row>
     <row r="8">
@@ -6151,10 +6151,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>343</v>
       </c>
       <c r="D8" t="n">
         <v>385</v>
@@ -6168,10 +6168,10 @@
         <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D9" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="n">
         <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11">
@@ -6199,7 +6199,7 @@
         <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12">
@@ -6210,7 +6210,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D12" t="n">
         <v>152</v>
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14">
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6280,7 +6280,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -6305,7 +6305,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
@@ -6322,7 +6322,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6339,7 +6339,7 @@
         <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4908</v>
+        <v>4178</v>
       </c>
       <c r="C2" t="n">
-        <v>6171</v>
+        <v>6537</v>
       </c>
       <c r="D2" t="n">
-        <v>33478</v>
+        <v>20048</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4046</v>
+        <v>3595</v>
       </c>
       <c r="C3" t="n">
-        <v>4511</v>
+        <v>3856</v>
       </c>
       <c r="D3" t="n">
-        <v>15962</v>
+        <v>10923</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2799</v>
+        <v>2564</v>
       </c>
       <c r="C4" t="n">
-        <v>4205</v>
+        <v>4002</v>
       </c>
       <c r="D4" t="n">
-        <v>7260</v>
+        <v>5256</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1661</v>
+        <v>1476</v>
       </c>
       <c r="C5" t="n">
-        <v>3092</v>
+        <v>3524</v>
       </c>
       <c r="D5" t="n">
-        <v>2677</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>877</v>
+        <v>765</v>
       </c>
       <c r="C6" t="n">
-        <v>2080</v>
+        <v>2704</v>
       </c>
       <c r="D6" t="n">
-        <v>1127</v>
+        <v>988</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>358</v>
+        <v>310</v>
       </c>
       <c r="C7" t="n">
-        <v>933</v>
+        <v>1553</v>
       </c>
       <c r="D7" t="n">
-        <v>617</v>
+        <v>600</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="C8" t="n">
-        <v>336</v>
+        <v>658</v>
       </c>
       <c r="D8" t="n">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>214</v>
+        <v>273</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" t="n">
         <v>191</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11">
@@ -6510,7 +6510,7 @@
         <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -6521,7 +6521,7 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D12" t="n">
         <v>155</v>
@@ -6538,7 +6538,7 @@
         <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -6563,7 +6563,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -6591,7 +6591,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_56_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_56_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5210</v>
+        <v>4312</v>
       </c>
       <c r="C2" t="n">
-        <v>12912</v>
+        <v>7818</v>
       </c>
       <c r="D2" t="n">
-        <v>19157</v>
+        <v>18331</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3191</v>
+        <v>3278</v>
       </c>
       <c r="C3" t="n">
-        <v>4542</v>
+        <v>8382</v>
       </c>
       <c r="D3" t="n">
-        <v>11541</v>
+        <v>13630</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2632</v>
+        <v>2467</v>
       </c>
       <c r="C4" t="n">
-        <v>3841</v>
+        <v>5523</v>
       </c>
       <c r="D4" t="n">
-        <v>6129</v>
+        <v>7616</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1738</v>
+        <v>1488</v>
       </c>
       <c r="C5" t="n">
-        <v>3660</v>
+        <v>4565</v>
       </c>
       <c r="D5" t="n">
-        <v>2536</v>
+        <v>3042</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1003</v>
+        <v>833</v>
       </c>
       <c r="C6" t="n">
-        <v>3084</v>
+        <v>3505</v>
       </c>
       <c r="D6" t="n">
-        <v>1160</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>461</v>
+        <v>399</v>
       </c>
       <c r="C7" t="n">
-        <v>2116</v>
+        <v>2162</v>
       </c>
       <c r="D7" t="n">
-        <v>658</v>
+        <v>663</v>
       </c>
     </row>
     <row r="8">
@@ -864,10 +864,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>172</v>
+        <v>155</v>
       </c>
       <c r="C8" t="n">
-        <v>1072</v>
+        <v>1008</v>
       </c>
       <c r="D8" t="n">
         <v>432</v>
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>450</v>
+        <v>408</v>
       </c>
       <c r="D9" t="n">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="D10" t="n">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
         <v>76</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1049,7 +1049,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D21" t="n">
         <v>8</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6762</v>
+        <v>6082</v>
       </c>
       <c r="C2" t="n">
-        <v>18969</v>
+        <v>13689</v>
       </c>
       <c r="D2" t="n">
-        <v>16528</v>
+        <v>20121</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3327</v>
+        <v>3062</v>
       </c>
       <c r="C3" t="n">
-        <v>7404</v>
+        <v>7168</v>
       </c>
       <c r="D3" t="n">
-        <v>11801</v>
+        <v>13353</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2464</v>
+        <v>2406</v>
       </c>
       <c r="C4" t="n">
-        <v>4104</v>
+        <v>6699</v>
       </c>
       <c r="D4" t="n">
-        <v>6767</v>
+        <v>8365</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1882</v>
+        <v>1693</v>
       </c>
       <c r="C5" t="n">
-        <v>3633</v>
+        <v>4911</v>
       </c>
       <c r="D5" t="n">
-        <v>3045</v>
+        <v>3622</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1216</v>
+        <v>1007</v>
       </c>
       <c r="C6" t="n">
-        <v>3318</v>
+        <v>3905</v>
       </c>
       <c r="D6" t="n">
-        <v>1344</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>620</v>
+        <v>520</v>
       </c>
       <c r="C7" t="n">
-        <v>2530</v>
+        <v>2753</v>
       </c>
       <c r="D7" t="n">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>259</v>
+        <v>227</v>
       </c>
       <c r="C8" t="n">
-        <v>1531</v>
+        <v>1484</v>
       </c>
       <c r="D8" t="n">
-        <v>456</v>
+        <v>461</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="C9" t="n">
-        <v>707</v>
+        <v>654</v>
       </c>
       <c r="D9" t="n">
-        <v>323</v>
+        <v>317</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C10" t="n">
-        <v>318</v>
+        <v>290</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
@@ -1251,7 +1251,7 @@
         <v>108</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
         <v>82</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -1307,7 +1307,7 @@
         <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1360,7 +1360,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D21" t="n">
         <v>9</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9231</v>
+        <v>6231</v>
       </c>
       <c r="C2" t="n">
-        <v>18945</v>
+        <v>12253</v>
       </c>
       <c r="D2" t="n">
-        <v>19237</v>
+        <v>23313</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3838</v>
+        <v>3443</v>
       </c>
       <c r="C3" t="n">
-        <v>10818</v>
+        <v>8781</v>
       </c>
       <c r="D3" t="n">
-        <v>11631</v>
+        <v>13310</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2428</v>
+        <v>2277</v>
       </c>
       <c r="C4" t="n">
-        <v>5436</v>
+        <v>6693</v>
       </c>
       <c r="D4" t="n">
-        <v>7334</v>
+        <v>8748</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1889</v>
+        <v>1754</v>
       </c>
       <c r="C5" t="n">
-        <v>3726</v>
+        <v>5499</v>
       </c>
       <c r="D5" t="n">
-        <v>3459</v>
+        <v>4194</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1356</v>
+        <v>1161</v>
       </c>
       <c r="C6" t="n">
-        <v>3420</v>
+        <v>4276</v>
       </c>
       <c r="D6" t="n">
-        <v>1571</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>771</v>
+        <v>643</v>
       </c>
       <c r="C7" t="n">
-        <v>2828</v>
+        <v>3176</v>
       </c>
       <c r="D7" t="n">
-        <v>799</v>
+        <v>833</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>355</v>
+        <v>298</v>
       </c>
       <c r="C8" t="n">
-        <v>1931</v>
+        <v>1953</v>
       </c>
       <c r="D8" t="n">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>140</v>
+        <v>121</v>
       </c>
       <c r="C9" t="n">
-        <v>1014</v>
+        <v>962</v>
       </c>
       <c r="D9" t="n">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C10" t="n">
-        <v>459</v>
+        <v>415</v>
       </c>
       <c r="D10" t="n">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>235</v>
+        <v>217</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -1545,7 +1545,7 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D12" t="n">
         <v>165</v>
@@ -1556,10 +1556,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
         <v>128</v>
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
         <v>89</v>
       </c>
       <c r="D14" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,7 +1671,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8211</v>
+        <v>5754</v>
       </c>
       <c r="C2" t="n">
-        <v>12731</v>
+        <v>8430</v>
       </c>
       <c r="D2" t="n">
-        <v>15836</v>
+        <v>19289</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4521</v>
+        <v>4110</v>
       </c>
       <c r="C3" t="n">
-        <v>15002</v>
+        <v>12629</v>
       </c>
       <c r="D3" t="n">
-        <v>12901</v>
+        <v>14826</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1745</v>
+        <v>1620</v>
       </c>
       <c r="C4" t="n">
-        <v>6603</v>
+        <v>8877</v>
       </c>
       <c r="D4" t="n">
-        <v>7215</v>
+        <v>8609</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1252</v>
+        <v>1072</v>
       </c>
       <c r="C5" t="n">
-        <v>3351</v>
+        <v>4190</v>
       </c>
       <c r="D5" t="n">
-        <v>2502</v>
+        <v>2848</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>712</v>
+        <v>594</v>
       </c>
       <c r="C6" t="n">
-        <v>2771</v>
+        <v>3112</v>
       </c>
       <c r="D6" t="n">
-        <v>783</v>
+        <v>816</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>328</v>
+        <v>275</v>
       </c>
       <c r="C7" t="n">
-        <v>1892</v>
+        <v>1913</v>
       </c>
       <c r="D7" t="n">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="C8" t="n">
-        <v>993</v>
+        <v>942</v>
       </c>
       <c r="D8" t="n">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>449</v>
+        <v>406</v>
       </c>
       <c r="D9" t="n">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>230</v>
+        <v>212</v>
       </c>
       <c r="D10" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11">
@@ -1842,7 +1842,7 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
         <v>161</v>
@@ -1853,10 +1853,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
         <v>125</v>
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
         <v>87</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,7 +1968,7 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D20" t="n">
         <v>10</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4756</v>
+        <v>3459</v>
       </c>
       <c r="C2" t="n">
-        <v>6089</v>
+        <v>3557</v>
       </c>
       <c r="D2" t="n">
-        <v>11577</v>
+        <v>13532</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5235</v>
+        <v>4152</v>
       </c>
       <c r="C3" t="n">
-        <v>12641</v>
+        <v>9743</v>
       </c>
       <c r="D3" t="n">
-        <v>12557</v>
+        <v>14721</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2424</v>
+        <v>2239</v>
       </c>
       <c r="C4" t="n">
-        <v>10670</v>
+        <v>10762</v>
       </c>
       <c r="D4" t="n">
-        <v>8007</v>
+        <v>9325</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1366</v>
+        <v>1193</v>
       </c>
       <c r="C5" t="n">
-        <v>4784</v>
+        <v>6193</v>
       </c>
       <c r="D5" t="n">
-        <v>3062</v>
+        <v>3535</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>853</v>
+        <v>708</v>
       </c>
       <c r="C6" t="n">
-        <v>3113</v>
+        <v>3634</v>
       </c>
       <c r="D6" t="n">
-        <v>961</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>309</v>
+        <v>258</v>
       </c>
       <c r="C7" t="n">
-        <v>2299</v>
+        <v>2398</v>
       </c>
       <c r="D7" t="n">
-        <v>522</v>
+        <v>527</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="C8" t="n">
-        <v>1280</v>
+        <v>1227</v>
       </c>
       <c r="D8" t="n">
-        <v>340</v>
+        <v>334</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C9" t="n">
-        <v>511</v>
+        <v>453</v>
       </c>
       <c r="D9" t="n">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>244</v>
+        <v>228</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -2150,10 +2150,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
         <v>167</v>
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,7 +2265,7 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D19" t="n">
         <v>9</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4023</v>
+        <v>4343</v>
       </c>
       <c r="C2" t="n">
-        <v>8699</v>
+        <v>10495</v>
       </c>
       <c r="D2" t="n">
-        <v>10489</v>
+        <v>17935</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4267</v>
+        <v>3249</v>
       </c>
       <c r="C3" t="n">
-        <v>8479</v>
+        <v>6127</v>
       </c>
       <c r="D3" t="n">
-        <v>11672</v>
+        <v>13570</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3088</v>
+        <v>2633</v>
       </c>
       <c r="C4" t="n">
-        <v>11413</v>
+        <v>10049</v>
       </c>
       <c r="D4" t="n">
-        <v>8506</v>
+        <v>9922</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1613</v>
+        <v>1441</v>
       </c>
       <c r="C5" t="n">
-        <v>7453</v>
+        <v>8169</v>
       </c>
       <c r="D5" t="n">
-        <v>3728</v>
+        <v>4316</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>982</v>
+        <v>830</v>
       </c>
       <c r="C6" t="n">
-        <v>3866</v>
+        <v>4764</v>
       </c>
       <c r="D6" t="n">
-        <v>1250</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>462</v>
+        <v>380</v>
       </c>
       <c r="C7" t="n">
-        <v>2671</v>
+        <v>2941</v>
       </c>
       <c r="D7" t="n">
-        <v>576</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="C8" t="n">
-        <v>1701</v>
+        <v>1697</v>
       </c>
       <c r="D8" t="n">
-        <v>359</v>
+        <v>355</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>802</v>
+        <v>737</v>
       </c>
       <c r="D9" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>340</v>
+        <v>307</v>
       </c>
       <c r="D10" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -2461,10 +2461,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="D11" t="n">
         <v>170</v>
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D12" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D15" t="n">
         <v>48</v>
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D16" t="n">
         <v>36</v>
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2392</v>
+        <v>2575</v>
       </c>
       <c r="C2" t="n">
-        <v>4071</v>
+        <v>4981</v>
       </c>
       <c r="D2" t="n">
-        <v>7322</v>
+        <v>12532</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4096</v>
+        <v>3381</v>
       </c>
       <c r="C3" t="n">
-        <v>8295</v>
+        <v>7383</v>
       </c>
       <c r="D3" t="n">
-        <v>11287</v>
+        <v>13719</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3401</v>
+        <v>2882</v>
       </c>
       <c r="C4" t="n">
-        <v>11313</v>
+        <v>9562</v>
       </c>
       <c r="D4" t="n">
-        <v>8965</v>
+        <v>10453</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1700</v>
+        <v>1489</v>
       </c>
       <c r="C5" t="n">
-        <v>9434</v>
+        <v>9881</v>
       </c>
       <c r="D5" t="n">
-        <v>3922</v>
+        <v>4535</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>826</v>
+        <v>680</v>
       </c>
       <c r="C6" t="n">
-        <v>4782</v>
+        <v>5606</v>
       </c>
       <c r="D6" t="n">
-        <v>1231</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>122</v>
       </c>
       <c r="C7" t="n">
-        <v>2903</v>
+        <v>3095</v>
       </c>
       <c r="D7" t="n">
-        <v>578</v>
+        <v>585</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C8" t="n">
-        <v>1302</v>
+        <v>1221</v>
       </c>
       <c r="D8" t="n">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>333</v>
+        <v>300</v>
       </c>
       <c r="D9" t="n">
-        <v>288</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10">
@@ -2758,10 +2758,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="D10" t="n">
         <v>166</v>
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D11" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
         <v>35</v>
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2659</v>
+        <v>3353</v>
       </c>
       <c r="C2" t="n">
-        <v>6586</v>
+        <v>9401</v>
       </c>
       <c r="D2" t="n">
-        <v>12362</v>
+        <v>14274</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2913</v>
+        <v>2609</v>
       </c>
       <c r="C3" t="n">
-        <v>5689</v>
+        <v>5638</v>
       </c>
       <c r="D3" t="n">
-        <v>10097</v>
+        <v>12667</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3244</v>
+        <v>2690</v>
       </c>
       <c r="C4" t="n">
-        <v>9766</v>
+        <v>8450</v>
       </c>
       <c r="D4" t="n">
-        <v>9049</v>
+        <v>10636</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2098</v>
+        <v>1808</v>
       </c>
       <c r="C5" t="n">
-        <v>10158</v>
+        <v>9537</v>
       </c>
       <c r="D5" t="n">
-        <v>4528</v>
+        <v>5249</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1044</v>
+        <v>891</v>
       </c>
       <c r="C6" t="n">
-        <v>6706</v>
+        <v>7430</v>
       </c>
       <c r="D6" t="n">
-        <v>1576</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>311</v>
+        <v>253</v>
       </c>
       <c r="C7" t="n">
-        <v>3666</v>
+        <v>4083</v>
       </c>
       <c r="D7" t="n">
-        <v>660</v>
+        <v>667</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C8" t="n">
-        <v>1920</v>
+        <v>1905</v>
       </c>
       <c r="D8" t="n">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>643</v>
+        <v>597</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10">
@@ -3069,10 +3069,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>237</v>
+        <v>219</v>
       </c>
       <c r="D10" t="n">
         <v>175</v>
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3103,7 +3103,7 @@
         <v>81</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>44</v>
+      </c>
+      <c r="D14" t="n">
         <v>46</v>
-      </c>
-      <c r="D14" t="n">
-        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D15" t="n">
         <v>33</v>
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D17" t="n">
         <v>9</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1874</v>
+        <v>2261</v>
       </c>
       <c r="C2" t="n">
-        <v>3609</v>
+        <v>6433</v>
       </c>
       <c r="D2" t="n">
-        <v>9143</v>
+        <v>10917</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2485</v>
+        <v>2490</v>
       </c>
       <c r="C3" t="n">
-        <v>5540</v>
+        <v>6427</v>
       </c>
       <c r="D3" t="n">
-        <v>9916</v>
+        <v>12178</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2875</v>
+        <v>2455</v>
       </c>
       <c r="C4" t="n">
-        <v>8145</v>
+        <v>7410</v>
       </c>
       <c r="D4" t="n">
-        <v>8991</v>
+        <v>10668</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2313</v>
+        <v>1968</v>
       </c>
       <c r="C5" t="n">
-        <v>10197</v>
+        <v>9329</v>
       </c>
       <c r="D5" t="n">
-        <v>4911</v>
+        <v>5759</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1223</v>
+        <v>1028</v>
       </c>
       <c r="C6" t="n">
-        <v>8017</v>
+        <v>8353</v>
       </c>
       <c r="D6" t="n">
-        <v>1858</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>278</v>
+        <v>227</v>
       </c>
       <c r="C7" t="n">
-        <v>4631</v>
+        <v>5115</v>
       </c>
       <c r="D7" t="n">
-        <v>729</v>
+        <v>745</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="C8" t="n">
-        <v>2376</v>
+        <v>2406</v>
       </c>
       <c r="D8" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>724</v>
+        <v>655</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>241</v>
+        <v>224</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
         <v>136</v>
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D12" t="n">
         <v>92</v>
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D14" t="n">
         <v>36</v>
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2918</v>
+        <v>2397</v>
       </c>
       <c r="C2" t="n">
-        <v>12582</v>
+        <v>10130</v>
       </c>
       <c r="D2" t="n">
-        <v>11376</v>
+        <v>17903</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1915</v>
+        <v>2033</v>
       </c>
       <c r="C3" t="n">
-        <v>4301</v>
+        <v>5791</v>
       </c>
       <c r="D3" t="n">
-        <v>9188</v>
+        <v>11364</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2382</v>
+        <v>2143</v>
       </c>
       <c r="C4" t="n">
-        <v>6900</v>
+        <v>6859</v>
       </c>
       <c r="D4" t="n">
-        <v>8850</v>
+        <v>10444</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2304</v>
+        <v>1942</v>
       </c>
       <c r="C5" t="n">
-        <v>9177</v>
+        <v>8398</v>
       </c>
       <c r="D5" t="n">
-        <v>5310</v>
+        <v>6243</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1466</v>
+        <v>1238</v>
       </c>
       <c r="C6" t="n">
-        <v>8767</v>
+        <v>8642</v>
       </c>
       <c r="D6" t="n">
-        <v>2215</v>
+        <v>2483</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>500</v>
+        <v>415</v>
       </c>
       <c r="C7" t="n">
-        <v>5856</v>
+        <v>6255</v>
       </c>
       <c r="D7" t="n">
-        <v>854</v>
+        <v>890</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="C8" t="n">
-        <v>3171</v>
+        <v>3307</v>
       </c>
       <c r="D8" t="n">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>1241</v>
+        <v>1210</v>
       </c>
       <c r="D9" t="n">
-        <v>301</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>387</v>
+        <v>348</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="D11" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D12" t="n">
         <v>94</v>
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3750,7 +3750,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
         <v>36</v>
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4826</v>
+        <v>4711</v>
       </c>
       <c r="C2" t="n">
-        <v>10480</v>
+        <v>8700</v>
       </c>
       <c r="D2" t="n">
-        <v>10958</v>
+        <v>15555</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2111</v>
+        <v>1752</v>
       </c>
       <c r="C2" t="n">
-        <v>7347</v>
+        <v>5996</v>
       </c>
       <c r="D2" t="n">
-        <v>8463</v>
+        <v>13319</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2656</v>
+        <v>2616</v>
       </c>
       <c r="C3" t="n">
-        <v>6475</v>
+        <v>7287</v>
       </c>
       <c r="D3" t="n">
-        <v>10052</v>
+        <v>12714</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3324</v>
+        <v>2890</v>
       </c>
       <c r="C4" t="n">
-        <v>9990</v>
+        <v>9704</v>
       </c>
       <c r="D4" t="n">
-        <v>9175</v>
+        <v>10722</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1397</v>
+        <v>1161</v>
       </c>
       <c r="C5" t="n">
-        <v>12773</v>
+        <v>12265</v>
       </c>
       <c r="D5" t="n">
-        <v>4930</v>
+        <v>5735</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>462</v>
+        <v>383</v>
       </c>
       <c r="C6" t="n">
-        <v>7371</v>
+        <v>7654</v>
       </c>
       <c r="D6" t="n">
-        <v>1791</v>
+        <v>1959</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="C7" t="n">
-        <v>3107</v>
+        <v>3240</v>
       </c>
       <c r="D7" t="n">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C8" t="n">
-        <v>1216</v>
+        <v>1185</v>
       </c>
       <c r="D8" t="n">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>379</v>
+        <v>341</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11">
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D11" t="n">
         <v>92</v>
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D13" t="n">
         <v>35</v>
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6915</v>
+        <v>5994</v>
       </c>
       <c r="C2" t="n">
-        <v>6147</v>
+        <v>7781</v>
       </c>
       <c r="D2" t="n">
-        <v>17464</v>
+        <v>16092</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2051</v>
+        <v>2003</v>
       </c>
       <c r="C3" t="n">
-        <v>5281</v>
+        <v>4384</v>
       </c>
       <c r="D3" t="n">
-        <v>2480</v>
+        <v>3252</v>
       </c>
     </row>
     <row r="4">
@@ -4557,7 +4557,7 @@
         <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4571,7 +4571,7 @@
         <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="D6" t="n">
         <v>816</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5273</v>
+        <v>3961</v>
       </c>
       <c r="C2" t="n">
-        <v>5594</v>
+        <v>6821</v>
       </c>
       <c r="D2" t="n">
-        <v>18101</v>
+        <v>25247</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3677</v>
+        <v>3281</v>
       </c>
       <c r="C3" t="n">
-        <v>4976</v>
+        <v>5438</v>
       </c>
       <c r="D3" t="n">
-        <v>4814</v>
+        <v>5169</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>925</v>
+        <v>904</v>
       </c>
       <c r="C4" t="n">
-        <v>3138</v>
+        <v>2613</v>
       </c>
       <c r="D4" t="n">
-        <v>1681</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D5" t="n">
         <v>1198</v>
@@ -4896,7 +4896,7 @@
         <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="D7" t="n">
         <v>584</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5025,7 +5025,7 @@
         <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>67</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4560</v>
+        <v>3842</v>
       </c>
       <c r="C2" t="n">
-        <v>7054</v>
+        <v>7782</v>
       </c>
       <c r="D2" t="n">
-        <v>19523</v>
+        <v>22411</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3664</v>
+        <v>2978</v>
       </c>
       <c r="C3" t="n">
-        <v>4598</v>
+        <v>5412</v>
       </c>
       <c r="D3" t="n">
-        <v>6593</v>
+        <v>8009</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1952</v>
+        <v>1777</v>
       </c>
       <c r="C4" t="n">
-        <v>4113</v>
+        <v>4106</v>
       </c>
       <c r="D4" t="n">
-        <v>2231</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="C5" t="n">
-        <v>1811</v>
+        <v>1525</v>
       </c>
       <c r="D5" t="n">
-        <v>1238</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="6">
@@ -5193,7 +5193,7 @@
         <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D6" t="n">
         <v>908</v>
@@ -5207,7 +5207,7 @@
         <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D7" t="n">
         <v>626</v>
@@ -5221,7 +5221,7 @@
         <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D8" t="n">
         <v>454</v>
@@ -5316,7 +5316,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>76</v>
@@ -5336,7 +5336,7 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5529</v>
+        <v>4258</v>
       </c>
       <c r="C2" t="n">
-        <v>4803</v>
+        <v>8413</v>
       </c>
       <c r="D2" t="n">
-        <v>20406</v>
+        <v>31211</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3363</v>
+        <v>2783</v>
       </c>
       <c r="C3" t="n">
-        <v>5102</v>
+        <v>5772</v>
       </c>
       <c r="D3" t="n">
-        <v>8094</v>
+        <v>9634</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2350</v>
+        <v>1999</v>
       </c>
       <c r="C4" t="n">
-        <v>4288</v>
+        <v>4722</v>
       </c>
       <c r="D4" t="n">
-        <v>2958</v>
+        <v>3365</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>971</v>
+        <v>904</v>
       </c>
       <c r="C5" t="n">
-        <v>2966</v>
+        <v>2831</v>
       </c>
       <c r="D5" t="n">
-        <v>1360</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="C6" t="n">
-        <v>1050</v>
+        <v>907</v>
       </c>
       <c r="D6" t="n">
-        <v>952</v>
+        <v>957</v>
       </c>
     </row>
     <row r="7">
@@ -5518,7 +5518,7 @@
         <v>143</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D7" t="n">
         <v>660</v>
@@ -5532,7 +5532,7 @@
         <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D8" t="n">
         <v>478</v>
@@ -5647,7 +5647,7 @@
         <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5987</v>
+        <v>6370</v>
       </c>
       <c r="C2" t="n">
-        <v>5518</v>
+        <v>6001</v>
       </c>
       <c r="D2" t="n">
-        <v>19455</v>
+        <v>28085</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3206</v>
+        <v>2544</v>
       </c>
       <c r="C3" t="n">
-        <v>4054</v>
+        <v>5816</v>
       </c>
       <c r="D3" t="n">
-        <v>8839</v>
+        <v>11510</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1775</v>
+        <v>1486</v>
       </c>
       <c r="C4" t="n">
-        <v>3879</v>
+        <v>4292</v>
       </c>
       <c r="D4" t="n">
-        <v>3318</v>
+        <v>3844</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>853</v>
+        <v>750</v>
       </c>
       <c r="C5" t="n">
-        <v>2643</v>
+        <v>2783</v>
       </c>
       <c r="D5" t="n">
-        <v>1281</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>287</v>
+        <v>271</v>
       </c>
       <c r="C6" t="n">
-        <v>1358</v>
+        <v>1245</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>787</v>
       </c>
     </row>
     <row r="7">
@@ -5826,10 +5826,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C7" t="n">
-        <v>443</v>
+        <v>398</v>
       </c>
       <c r="D7" t="n">
         <v>514</v>
@@ -5843,7 +5843,7 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D8" t="n">
         <v>360</v>
@@ -5857,7 +5857,7 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D9" t="n">
         <v>270</v>
@@ -5868,10 +5868,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
         <v>235</v>
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12">
@@ -5902,7 +5902,7 @@
         <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13">
@@ -5941,7 +5941,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -5983,7 +5983,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6025,7 +6025,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4935</v>
+        <v>4827</v>
       </c>
       <c r="C2" t="n">
-        <v>4650</v>
+        <v>9218</v>
       </c>
       <c r="D2" t="n">
-        <v>20408</v>
+        <v>21551</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3822</v>
+        <v>3690</v>
       </c>
       <c r="C3" t="n">
-        <v>4221</v>
+        <v>5090</v>
       </c>
       <c r="D3" t="n">
-        <v>9971</v>
+        <v>13447</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2188</v>
+        <v>1747</v>
       </c>
       <c r="C4" t="n">
-        <v>3904</v>
+        <v>5124</v>
       </c>
       <c r="D4" t="n">
-        <v>4298</v>
+        <v>5235</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1165</v>
+        <v>999</v>
       </c>
       <c r="C5" t="n">
-        <v>3286</v>
+        <v>3608</v>
       </c>
       <c r="D5" t="n">
-        <v>1652</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>531</v>
+        <v>472</v>
       </c>
       <c r="C6" t="n">
-        <v>2081</v>
+        <v>2100</v>
       </c>
       <c r="D6" t="n">
-        <v>855</v>
+        <v>888</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>962</v>
+        <v>870</v>
       </c>
       <c r="D7" t="n">
-        <v>560</v>
+        <v>554</v>
       </c>
     </row>
     <row r="8">
@@ -6154,7 +6154,7 @@
         <v>66</v>
       </c>
       <c r="C8" t="n">
-        <v>343</v>
+        <v>317</v>
       </c>
       <c r="D8" t="n">
         <v>385</v>
@@ -6168,10 +6168,10 @@
         <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D9" t="n">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D10" t="n">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11">
@@ -6199,7 +6199,7 @@
         <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13">
@@ -6224,10 +6224,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14">
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6255,7 +6255,7 @@
         <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -6294,10 +6294,10 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6311,7 +6311,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6322,7 +6322,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6336,7 +6336,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4178</v>
+        <v>4515</v>
       </c>
       <c r="C2" t="n">
-        <v>6537</v>
+        <v>12793</v>
       </c>
       <c r="D2" t="n">
-        <v>20048</v>
+        <v>19355</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3595</v>
+        <v>3527</v>
       </c>
       <c r="C3" t="n">
-        <v>3856</v>
+        <v>6329</v>
       </c>
       <c r="D3" t="n">
-        <v>10923</v>
+        <v>13775</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2564</v>
+        <v>2297</v>
       </c>
       <c r="C4" t="n">
-        <v>4002</v>
+        <v>4998</v>
       </c>
       <c r="D4" t="n">
-        <v>5256</v>
+        <v>6652</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1476</v>
+        <v>1207</v>
       </c>
       <c r="C5" t="n">
-        <v>3524</v>
+        <v>4313</v>
       </c>
       <c r="D5" t="n">
-        <v>2068</v>
+        <v>2376</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>765</v>
+        <v>659</v>
       </c>
       <c r="C6" t="n">
-        <v>2704</v>
+        <v>2872</v>
       </c>
       <c r="D6" t="n">
-        <v>988</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>310</v>
+        <v>277</v>
       </c>
       <c r="C7" t="n">
-        <v>1553</v>
+        <v>1508</v>
       </c>
       <c r="D7" t="n">
-        <v>600</v>
+        <v>607</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C8" t="n">
-        <v>658</v>
+        <v>593</v>
       </c>
       <c r="D8" t="n">
-        <v>411</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>273</v>
+        <v>258</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11">
@@ -6507,7 +6507,7 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
         <v>202</v>
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14">
@@ -6552,7 +6552,7 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -6566,7 +6566,7 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6608,7 +6608,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6633,7 +6633,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6647,7 +6647,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
         <v>7</v>

--- a/output/yearly_population_iteration_56_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_56_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4312</v>
+        <v>1145</v>
       </c>
       <c r="C2" t="n">
-        <v>7818</v>
+        <v>3361</v>
       </c>
       <c r="D2" t="n">
-        <v>18331</v>
+        <v>18007</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3278</v>
+        <v>1841</v>
       </c>
       <c r="C3" t="n">
-        <v>8382</v>
+        <v>6206</v>
       </c>
       <c r="D3" t="n">
-        <v>13630</v>
+        <v>20175</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2467</v>
+        <v>1119</v>
       </c>
       <c r="C4" t="n">
-        <v>5523</v>
+        <v>6497</v>
       </c>
       <c r="D4" t="n">
-        <v>7616</v>
+        <v>9506</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1488</v>
+        <v>493</v>
       </c>
       <c r="C5" t="n">
-        <v>4565</v>
+        <v>3718</v>
       </c>
       <c r="D5" t="n">
-        <v>3042</v>
+        <v>2693</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>833</v>
+        <v>203</v>
       </c>
       <c r="C6" t="n">
-        <v>3505</v>
+        <v>1243</v>
       </c>
       <c r="D6" t="n">
-        <v>1249</v>
+        <v>781</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>399</v>
+        <v>95</v>
       </c>
       <c r="C7" t="n">
-        <v>2162</v>
+        <v>503</v>
       </c>
       <c r="D7" t="n">
-        <v>663</v>
+        <v>492</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>155</v>
+        <v>73</v>
       </c>
       <c r="C8" t="n">
-        <v>1008</v>
+        <v>333</v>
       </c>
       <c r="D8" t="n">
-        <v>432</v>
+        <v>373</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>408</v>
+        <v>287</v>
       </c>
       <c r="D9" t="n">
-        <v>306</v>
+        <v>315</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>141</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6082</v>
+        <v>882</v>
       </c>
       <c r="C2" t="n">
-        <v>13689</v>
+        <v>11042</v>
       </c>
       <c r="D2" t="n">
-        <v>20121</v>
+        <v>17446</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3062</v>
+        <v>1286</v>
       </c>
       <c r="C3" t="n">
-        <v>7168</v>
+        <v>4121</v>
       </c>
       <c r="D3" t="n">
-        <v>13353</v>
+        <v>18425</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2406</v>
+        <v>1264</v>
       </c>
       <c r="C4" t="n">
-        <v>6699</v>
+        <v>6202</v>
       </c>
       <c r="D4" t="n">
-        <v>8365</v>
+        <v>11163</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1693</v>
+        <v>683</v>
       </c>
       <c r="C5" t="n">
-        <v>4911</v>
+        <v>5143</v>
       </c>
       <c r="D5" t="n">
-        <v>3622</v>
+        <v>3788</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1007</v>
+        <v>300</v>
       </c>
       <c r="C6" t="n">
-        <v>3905</v>
+        <v>2477</v>
       </c>
       <c r="D6" t="n">
-        <v>1507</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>520</v>
+        <v>128</v>
       </c>
       <c r="C7" t="n">
-        <v>2753</v>
+        <v>863</v>
       </c>
       <c r="D7" t="n">
-        <v>735</v>
+        <v>532</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>227</v>
+        <v>77</v>
       </c>
       <c r="C8" t="n">
-        <v>1484</v>
+        <v>412</v>
       </c>
       <c r="D8" t="n">
-        <v>461</v>
+        <v>390</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>88</v>
+        <v>56</v>
       </c>
       <c r="C9" t="n">
-        <v>654</v>
+        <v>311</v>
       </c>
       <c r="D9" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="C10" t="n">
-        <v>290</v>
+        <v>244</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>95</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>77</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6231</v>
+        <v>470</v>
       </c>
       <c r="C2" t="n">
-        <v>12253</v>
+        <v>4564</v>
       </c>
       <c r="D2" t="n">
-        <v>23313</v>
+        <v>11758</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3443</v>
+        <v>1127</v>
       </c>
       <c r="C3" t="n">
-        <v>8781</v>
+        <v>6662</v>
       </c>
       <c r="D3" t="n">
-        <v>13310</v>
+        <v>17798</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2277</v>
+        <v>1379</v>
       </c>
       <c r="C4" t="n">
-        <v>6693</v>
+        <v>5908</v>
       </c>
       <c r="D4" t="n">
-        <v>8748</v>
+        <v>12303</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1754</v>
+        <v>677</v>
       </c>
       <c r="C5" t="n">
-        <v>5499</v>
+        <v>6011</v>
       </c>
       <c r="D5" t="n">
-        <v>4194</v>
+        <v>4267</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1161</v>
+        <v>254</v>
       </c>
       <c r="C6" t="n">
-        <v>4276</v>
+        <v>3248</v>
       </c>
       <c r="D6" t="n">
-        <v>1756</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>643</v>
+        <v>71</v>
       </c>
       <c r="C7" t="n">
-        <v>3176</v>
+        <v>875</v>
       </c>
       <c r="D7" t="n">
-        <v>833</v>
+        <v>561</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>298</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>1953</v>
+        <v>450</v>
       </c>
       <c r="D8" t="n">
-        <v>486</v>
+        <v>434</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>121</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>962</v>
+        <v>239</v>
       </c>
       <c r="D9" t="n">
-        <v>332</v>
+        <v>368</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>415</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
-        <v>252</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>217</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>152</v>
+        <v>86</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>89</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>93</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5754</v>
+        <v>515</v>
       </c>
       <c r="C2" t="n">
-        <v>8430</v>
+        <v>5664</v>
       </c>
       <c r="D2" t="n">
-        <v>19289</v>
+        <v>13215</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4110</v>
+        <v>710</v>
       </c>
       <c r="C3" t="n">
-        <v>12629</v>
+        <v>4922</v>
       </c>
       <c r="D3" t="n">
-        <v>14826</v>
+        <v>15797</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1620</v>
+        <v>1127</v>
       </c>
       <c r="C4" t="n">
-        <v>8877</v>
+        <v>6239</v>
       </c>
       <c r="D4" t="n">
-        <v>8609</v>
+        <v>12878</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1072</v>
+        <v>870</v>
       </c>
       <c r="C5" t="n">
-        <v>4190</v>
+        <v>5892</v>
       </c>
       <c r="D5" t="n">
-        <v>2848</v>
+        <v>5448</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>594</v>
+        <v>387</v>
       </c>
       <c r="C6" t="n">
-        <v>3112</v>
+        <v>4578</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>275</v>
+        <v>121</v>
       </c>
       <c r="C7" t="n">
-        <v>1913</v>
+        <v>1938</v>
       </c>
       <c r="D7" t="n">
-        <v>476</v>
+        <v>627</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>111</v>
+        <v>55</v>
       </c>
       <c r="C8" t="n">
-        <v>942</v>
+        <v>629</v>
       </c>
       <c r="D8" t="n">
-        <v>325</v>
+        <v>450</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="C9" t="n">
-        <v>406</v>
+        <v>322</v>
       </c>
       <c r="D9" t="n">
-        <v>246</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
         <v>212</v>
       </c>
       <c r="D10" t="n">
-        <v>201</v>
+        <v>224</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>161</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>125</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>81</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
+        <v>66</v>
+      </c>
+      <c r="D15" t="n">
         <v>49</v>
-      </c>
-      <c r="D15" t="n">
-        <v>62</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>101</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3459</v>
+        <v>340</v>
       </c>
       <c r="C2" t="n">
-        <v>3557</v>
+        <v>3983</v>
       </c>
       <c r="D2" t="n">
-        <v>13532</v>
+        <v>9599</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4152</v>
+        <v>557</v>
       </c>
       <c r="C3" t="n">
-        <v>9743</v>
+        <v>4767</v>
       </c>
       <c r="D3" t="n">
-        <v>14721</v>
+        <v>14535</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2239</v>
+        <v>912</v>
       </c>
       <c r="C4" t="n">
-        <v>10762</v>
+        <v>5682</v>
       </c>
       <c r="D4" t="n">
-        <v>9325</v>
+        <v>13182</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1193</v>
+        <v>926</v>
       </c>
       <c r="C5" t="n">
-        <v>6193</v>
+        <v>6138</v>
       </c>
       <c r="D5" t="n">
-        <v>3535</v>
+        <v>6261</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>708</v>
+        <v>480</v>
       </c>
       <c r="C6" t="n">
-        <v>3634</v>
+        <v>5233</v>
       </c>
       <c r="D6" t="n">
-        <v>1025</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>258</v>
+        <v>136</v>
       </c>
       <c r="C7" t="n">
-        <v>2398</v>
+        <v>2846</v>
       </c>
       <c r="D7" t="n">
-        <v>527</v>
+        <v>708</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>95</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>1227</v>
+        <v>959</v>
       </c>
       <c r="D8" t="n">
-        <v>334</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>453</v>
+        <v>408</v>
       </c>
       <c r="D9" t="n">
-        <v>255</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>231</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4343</v>
+        <v>487</v>
       </c>
       <c r="C2" t="n">
-        <v>10495</v>
+        <v>10024</v>
       </c>
       <c r="D2" t="n">
-        <v>17935</v>
+        <v>12886</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3249</v>
+        <v>394</v>
       </c>
       <c r="C3" t="n">
-        <v>6127</v>
+        <v>3913</v>
       </c>
       <c r="D3" t="n">
-        <v>13570</v>
+        <v>12886</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2633</v>
+        <v>676</v>
       </c>
       <c r="C4" t="n">
-        <v>10049</v>
+        <v>5124</v>
       </c>
       <c r="D4" t="n">
-        <v>9922</v>
+        <v>13002</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1441</v>
+        <v>842</v>
       </c>
       <c r="C5" t="n">
-        <v>8169</v>
+        <v>5800</v>
       </c>
       <c r="D5" t="n">
-        <v>4316</v>
+        <v>7133</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>830</v>
+        <v>605</v>
       </c>
       <c r="C6" t="n">
-        <v>4764</v>
+        <v>5633</v>
       </c>
       <c r="D6" t="n">
-        <v>1372</v>
+        <v>2591</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>380</v>
+        <v>235</v>
       </c>
       <c r="C7" t="n">
-        <v>2941</v>
+        <v>3850</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>878</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>133</v>
+        <v>72</v>
       </c>
       <c r="C8" t="n">
-        <v>1697</v>
+        <v>1726</v>
       </c>
       <c r="D8" t="n">
-        <v>355</v>
+        <v>507</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="C9" t="n">
-        <v>737</v>
+        <v>617</v>
       </c>
       <c r="D9" t="n">
-        <v>264</v>
+        <v>386</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>307</v>
+        <v>296</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>188</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>103</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2575</v>
+        <v>327</v>
       </c>
       <c r="C2" t="n">
-        <v>4981</v>
+        <v>5212</v>
       </c>
       <c r="D2" t="n">
-        <v>12532</v>
+        <v>9278</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3381</v>
+        <v>588</v>
       </c>
       <c r="C3" t="n">
-        <v>7383</v>
+        <v>5924</v>
       </c>
       <c r="D3" t="n">
-        <v>13719</v>
+        <v>14025</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2882</v>
+        <v>1109</v>
       </c>
       <c r="C4" t="n">
-        <v>9562</v>
+        <v>7061</v>
       </c>
       <c r="D4" t="n">
-        <v>10453</v>
+        <v>13432</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1489</v>
+        <v>613</v>
       </c>
       <c r="C5" t="n">
-        <v>9881</v>
+        <v>8204</v>
       </c>
       <c r="D5" t="n">
-        <v>4535</v>
+        <v>6491</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>680</v>
+        <v>217</v>
       </c>
       <c r="C6" t="n">
-        <v>5606</v>
+        <v>5153</v>
       </c>
       <c r="D6" t="n">
-        <v>1340</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>122</v>
+        <v>66</v>
       </c>
       <c r="C7" t="n">
-        <v>3095</v>
+        <v>1691</v>
       </c>
       <c r="D7" t="n">
-        <v>585</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="C8" t="n">
-        <v>1221</v>
+        <v>604</v>
       </c>
       <c r="D8" t="n">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="D9" t="n">
-        <v>285</v>
+        <v>241</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>87</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>98</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3353</v>
+        <v>174</v>
       </c>
       <c r="C2" t="n">
-        <v>9401</v>
+        <v>3172</v>
       </c>
       <c r="D2" t="n">
-        <v>14274</v>
+        <v>7867</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2609</v>
+        <v>408</v>
       </c>
       <c r="C3" t="n">
-        <v>5638</v>
+        <v>4923</v>
       </c>
       <c r="D3" t="n">
-        <v>12667</v>
+        <v>12336</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2690</v>
+        <v>732</v>
       </c>
       <c r="C4" t="n">
-        <v>8450</v>
+        <v>6155</v>
       </c>
       <c r="D4" t="n">
-        <v>10636</v>
+        <v>12597</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1808</v>
+        <v>581</v>
       </c>
       <c r="C5" t="n">
-        <v>9537</v>
+        <v>6735</v>
       </c>
       <c r="D5" t="n">
-        <v>5249</v>
+        <v>6745</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>891</v>
+        <v>214</v>
       </c>
       <c r="C6" t="n">
-        <v>7430</v>
+        <v>5321</v>
       </c>
       <c r="D6" t="n">
-        <v>1765</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>253</v>
+        <v>54</v>
       </c>
       <c r="C7" t="n">
-        <v>4083</v>
+        <v>2248</v>
       </c>
       <c r="D7" t="n">
-        <v>667</v>
+        <v>634</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>59</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>1905</v>
+        <v>664</v>
       </c>
       <c r="D8" t="n">
-        <v>397</v>
+        <v>327</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>597</v>
+        <v>260</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>191</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>75</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>53</v>
       </c>
       <c r="D12" t="n">
-        <v>101</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2261</v>
+        <v>334</v>
       </c>
       <c r="C2" t="n">
-        <v>6433</v>
+        <v>5566</v>
       </c>
       <c r="D2" t="n">
-        <v>10917</v>
+        <v>7889</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2490</v>
+        <v>251</v>
       </c>
       <c r="C3" t="n">
-        <v>6427</v>
+        <v>3478</v>
       </c>
       <c r="D3" t="n">
-        <v>12178</v>
+        <v>10788</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2455</v>
+        <v>512</v>
       </c>
       <c r="C4" t="n">
-        <v>7410</v>
+        <v>5352</v>
       </c>
       <c r="D4" t="n">
-        <v>10668</v>
+        <v>12166</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1968</v>
+        <v>591</v>
       </c>
       <c r="C5" t="n">
-        <v>9329</v>
+        <v>6353</v>
       </c>
       <c r="D5" t="n">
-        <v>5759</v>
+        <v>7551</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1028</v>
+        <v>342</v>
       </c>
       <c r="C6" t="n">
-        <v>8353</v>
+        <v>5969</v>
       </c>
       <c r="D6" t="n">
-        <v>2046</v>
+        <v>2944</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>227</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>5115</v>
+        <v>3774</v>
       </c>
       <c r="D7" t="n">
-        <v>745</v>
+        <v>879</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="C8" t="n">
-        <v>2406</v>
+        <v>1399</v>
       </c>
       <c r="D8" t="n">
-        <v>412</v>
+        <v>368</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>655</v>
+        <v>436</v>
       </c>
       <c r="D9" t="n">
-        <v>288</v>
+        <v>207</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>224</v>
+        <v>182</v>
       </c>
       <c r="D10" t="n">
-        <v>180</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>128</v>
+        <v>96</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2397</v>
+        <v>258</v>
       </c>
       <c r="C2" t="n">
-        <v>10130</v>
+        <v>8203</v>
       </c>
       <c r="D2" t="n">
-        <v>17903</v>
+        <v>13550</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2033</v>
+        <v>239</v>
       </c>
       <c r="C3" t="n">
-        <v>5791</v>
+        <v>3962</v>
       </c>
       <c r="D3" t="n">
-        <v>11364</v>
+        <v>9628</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2143</v>
+        <v>344</v>
       </c>
       <c r="C4" t="n">
-        <v>6859</v>
+        <v>4253</v>
       </c>
       <c r="D4" t="n">
-        <v>10444</v>
+        <v>11558</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1942</v>
+        <v>510</v>
       </c>
       <c r="C5" t="n">
-        <v>8398</v>
+        <v>5730</v>
       </c>
       <c r="D5" t="n">
-        <v>6243</v>
+        <v>8074</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1238</v>
+        <v>414</v>
       </c>
       <c r="C6" t="n">
-        <v>8642</v>
+        <v>6088</v>
       </c>
       <c r="D6" t="n">
-        <v>2483</v>
+        <v>3583</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>415</v>
+        <v>183</v>
       </c>
       <c r="C7" t="n">
-        <v>6255</v>
+        <v>4783</v>
       </c>
       <c r="D7" t="n">
-        <v>890</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>85</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>3307</v>
+        <v>2445</v>
       </c>
       <c r="D8" t="n">
-        <v>443</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>1210</v>
+        <v>841</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>224</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>348</v>
+        <v>283</v>
       </c>
       <c r="D10" t="n">
-        <v>189</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4711</v>
+        <v>2131</v>
       </c>
       <c r="C2" t="n">
-        <v>8700</v>
+        <v>4728</v>
       </c>
       <c r="D2" t="n">
-        <v>15555</v>
+        <v>18438</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1752</v>
+        <v>247</v>
       </c>
       <c r="C2" t="n">
-        <v>5996</v>
+        <v>18626</v>
       </c>
       <c r="D2" t="n">
-        <v>13319</v>
+        <v>16786</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2616</v>
+        <v>206</v>
       </c>
       <c r="C3" t="n">
-        <v>7287</v>
+        <v>5165</v>
       </c>
       <c r="D3" t="n">
-        <v>12714</v>
+        <v>9498</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2890</v>
+        <v>261</v>
       </c>
       <c r="C4" t="n">
-        <v>9704</v>
+        <v>3992</v>
       </c>
       <c r="D4" t="n">
-        <v>10722</v>
+        <v>10799</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1161</v>
+        <v>408</v>
       </c>
       <c r="C5" t="n">
-        <v>12265</v>
+        <v>4958</v>
       </c>
       <c r="D5" t="n">
-        <v>5735</v>
+        <v>8363</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>383</v>
+        <v>423</v>
       </c>
       <c r="C6" t="n">
-        <v>7654</v>
+        <v>5821</v>
       </c>
       <c r="D6" t="n">
-        <v>1959</v>
+        <v>4182</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>78</v>
+        <v>245</v>
       </c>
       <c r="C7" t="n">
-        <v>3240</v>
+        <v>5331</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="C8" t="n">
-        <v>1185</v>
+        <v>3383</v>
       </c>
       <c r="D8" t="n">
-        <v>291</v>
+        <v>537</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>341</v>
+        <v>1445</v>
       </c>
       <c r="D9" t="n">
-        <v>185</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>490</v>
       </c>
       <c r="D10" t="n">
-        <v>134</v>
+        <v>159</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>86</v>
+        <v>181</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>48</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>61</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>31</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5994</v>
+        <v>3488</v>
       </c>
       <c r="C2" t="n">
-        <v>7781</v>
+        <v>6054</v>
       </c>
       <c r="D2" t="n">
-        <v>16092</v>
+        <v>36925</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2003</v>
+        <v>707</v>
       </c>
       <c r="C3" t="n">
-        <v>4384</v>
+        <v>1867</v>
       </c>
       <c r="D3" t="n">
-        <v>3252</v>
+        <v>3121</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>334</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>454</v>
+        <v>360</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3961</v>
+        <v>2828</v>
       </c>
       <c r="C2" t="n">
-        <v>6821</v>
+        <v>7078</v>
       </c>
       <c r="D2" t="n">
-        <v>25247</v>
+        <v>35070</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3281</v>
+        <v>1783</v>
       </c>
       <c r="C3" t="n">
-        <v>5438</v>
+        <v>3775</v>
       </c>
       <c r="D3" t="n">
-        <v>5169</v>
+        <v>8835</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>904</v>
+        <v>354</v>
       </c>
       <c r="C4" t="n">
-        <v>2613</v>
+        <v>1212</v>
       </c>
       <c r="D4" t="n">
-        <v>1836</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>340</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>113</v>
       </c>
       <c r="C7" t="n">
-        <v>406</v>
+        <v>324</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>244</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3842</v>
+        <v>2481</v>
       </c>
       <c r="C2" t="n">
-        <v>7782</v>
+        <v>5096</v>
       </c>
       <c r="D2" t="n">
-        <v>22411</v>
+        <v>41114</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2978</v>
+        <v>1905</v>
       </c>
       <c r="C3" t="n">
-        <v>5412</v>
+        <v>4887</v>
       </c>
       <c r="D3" t="n">
-        <v>8009</v>
+        <v>12592</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1777</v>
+        <v>940</v>
       </c>
       <c r="C4" t="n">
-        <v>4106</v>
+        <v>2712</v>
       </c>
       <c r="D4" t="n">
-        <v>2420</v>
+        <v>3128</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>424</v>
+        <v>198</v>
       </c>
       <c r="C5" t="n">
-        <v>1525</v>
+        <v>782</v>
       </c>
       <c r="D5" t="n">
-        <v>1266</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>111</v>
       </c>
       <c r="C6" t="n">
-        <v>305</v>
+        <v>262</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>794</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>116</v>
       </c>
       <c r="C7" t="n">
-        <v>403</v>
+        <v>332</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>357</v>
+        <v>286</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>216</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>174</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>194</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4258</v>
+        <v>1727</v>
       </c>
       <c r="C2" t="n">
-        <v>8413</v>
+        <v>5729</v>
       </c>
       <c r="D2" t="n">
-        <v>31211</v>
+        <v>35750</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2783</v>
+        <v>1800</v>
       </c>
       <c r="C3" t="n">
-        <v>5772</v>
+        <v>4328</v>
       </c>
       <c r="D3" t="n">
-        <v>9634</v>
+        <v>16248</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1999</v>
+        <v>1211</v>
       </c>
       <c r="C4" t="n">
-        <v>4722</v>
+        <v>3887</v>
       </c>
       <c r="D4" t="n">
-        <v>3365</v>
+        <v>4849</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>904</v>
+        <v>483</v>
       </c>
       <c r="C5" t="n">
-        <v>2831</v>
+        <v>1821</v>
       </c>
       <c r="D5" t="n">
-        <v>1414</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>247</v>
+        <v>141</v>
       </c>
       <c r="C6" t="n">
-        <v>907</v>
+        <v>533</v>
       </c>
       <c r="D6" t="n">
-        <v>957</v>
+        <v>846</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>106</v>
       </c>
       <c r="C7" t="n">
-        <v>353</v>
+        <v>292</v>
       </c>
       <c r="D7" t="n">
-        <v>660</v>
+        <v>585</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="C8" t="n">
-        <v>378</v>
+        <v>309</v>
       </c>
       <c r="D8" t="n">
-        <v>478</v>
+        <v>422</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>250</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>160</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>254</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6370</v>
+        <v>2021</v>
       </c>
       <c r="C2" t="n">
-        <v>6001</v>
+        <v>4063</v>
       </c>
       <c r="D2" t="n">
-        <v>28085</v>
+        <v>27683</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2544</v>
+        <v>1462</v>
       </c>
       <c r="C3" t="n">
-        <v>5816</v>
+        <v>4394</v>
       </c>
       <c r="D3" t="n">
-        <v>11510</v>
+        <v>18068</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1486</v>
+        <v>1288</v>
       </c>
       <c r="C4" t="n">
-        <v>4292</v>
+        <v>4043</v>
       </c>
       <c r="D4" t="n">
-        <v>3844</v>
+        <v>6780</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>750</v>
+        <v>714</v>
       </c>
       <c r="C5" t="n">
-        <v>2783</v>
+        <v>2836</v>
       </c>
       <c r="D5" t="n">
-        <v>1372</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="6">
@@ -5815,10 +5815,10 @@
         <v>271</v>
       </c>
       <c r="C6" t="n">
-        <v>1245</v>
+        <v>1182</v>
       </c>
       <c r="D6" t="n">
-        <v>787</v>
+        <v>939</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>85</v>
+        <v>113</v>
       </c>
       <c r="C7" t="n">
-        <v>398</v>
+        <v>412</v>
       </c>
       <c r="D7" t="n">
-        <v>514</v>
+        <v>616</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>300</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>444</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>196</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>347</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>218</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>172</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>260</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>145</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>205</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>119</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,10 +6022,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>76</v>
+        <v>132</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4827</v>
+        <v>2557</v>
       </c>
       <c r="C2" t="n">
-        <v>9218</v>
+        <v>11074</v>
       </c>
       <c r="D2" t="n">
-        <v>21551</v>
+        <v>33427</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3690</v>
+        <v>1408</v>
       </c>
       <c r="C3" t="n">
-        <v>5090</v>
+        <v>3705</v>
       </c>
       <c r="D3" t="n">
-        <v>13447</v>
+        <v>18209</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1747</v>
+        <v>1173</v>
       </c>
       <c r="C4" t="n">
-        <v>5124</v>
+        <v>4137</v>
       </c>
       <c r="D4" t="n">
-        <v>5235</v>
+        <v>8524</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>999</v>
+        <v>861</v>
       </c>
       <c r="C5" t="n">
-        <v>3608</v>
+        <v>3340</v>
       </c>
       <c r="D5" t="n">
-        <v>1828</v>
+        <v>2687</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>472</v>
+        <v>420</v>
       </c>
       <c r="C6" t="n">
-        <v>2100</v>
+        <v>1963</v>
       </c>
       <c r="D6" t="n">
-        <v>888</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C7" t="n">
-        <v>870</v>
+        <v>774</v>
       </c>
       <c r="D7" t="n">
-        <v>554</v>
+        <v>654</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>317</v>
+        <v>350</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>466</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="C9" t="n">
-        <v>209</v>
+        <v>284</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n">
-        <v>171</v>
+        <v>242</v>
       </c>
       <c r="D10" t="n">
-        <v>236</v>
+        <v>308</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>264</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>153</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>128</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6333,10 +6333,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>84</v>
+        <v>144</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4515</v>
+        <v>2273</v>
       </c>
       <c r="C2" t="n">
-        <v>12793</v>
+        <v>6821</v>
       </c>
       <c r="D2" t="n">
-        <v>19355</v>
+        <v>26288</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3527</v>
+        <v>1971</v>
       </c>
       <c r="C3" t="n">
-        <v>6329</v>
+        <v>6984</v>
       </c>
       <c r="D3" t="n">
-        <v>13775</v>
+        <v>20306</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2297</v>
+        <v>795</v>
       </c>
       <c r="C4" t="n">
-        <v>4998</v>
+        <v>5787</v>
       </c>
       <c r="D4" t="n">
-        <v>6652</v>
+        <v>7589</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1207</v>
+        <v>388</v>
       </c>
       <c r="C5" t="n">
-        <v>4313</v>
+        <v>1923</v>
       </c>
       <c r="D5" t="n">
-        <v>2376</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>659</v>
+        <v>151</v>
       </c>
       <c r="C6" t="n">
-        <v>2872</v>
+        <v>758</v>
       </c>
       <c r="D6" t="n">
-        <v>1047</v>
+        <v>640</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>277</v>
+        <v>85</v>
       </c>
       <c r="C7" t="n">
-        <v>1508</v>
+        <v>343</v>
       </c>
       <c r="D7" t="n">
-        <v>607</v>
+        <v>456</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>593</v>
+        <v>278</v>
       </c>
       <c r="D8" t="n">
-        <v>405</v>
+        <v>349</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>258</v>
+        <v>237</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D10" t="n">
-        <v>238</v>
+        <v>258</v>
       </c>
     </row>
     <row r="11">
@@ -6504,7 +6504,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
         <v>149</v>
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>144</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
